--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NandanSH\eclipse-workspace\Framework.v1\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BD32A8-B06A-439B-99DA-0DA0CC146E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BB50FF-166B-4649-ADDF-D754A7AB1CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="17430" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,18 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
-    <t>username</t>
+    <t>hegdenandan013@gmail.com</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
   <si>
     <t>password</t>
   </si>
   <si>
-    <t>hegdenandan013@gmail.com</t>
+    <t>userName</t>
   </si>
   <si>
-    <t>Test</t>
+    <t>ASDFTYHGFDSGHGFDFGHFD</t>
   </si>
 </sst>
 </file>
@@ -365,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -373,23 +376,32 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{41A2A964-FC9C-4B93-8801-2A9062BE774F}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{E701D300-0946-4A12-A216-676422D061B7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
